--- a/xlsx/dex.xlsx
+++ b/xlsx/dex.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="18100" yWindow="1060" windowWidth="23760" windowHeight="23340" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/xlsx/dex.xlsx
+++ b/xlsx/dex.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="18100" yWindow="1060" windowWidth="23760" windowHeight="23340" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -7310,7 +7310,7 @@
       <c r="G119" s="5" t="n"/>
       <c r="H119" s="1" t="inlineStr">
         <is>
-          <t>金鱼王之所以会用;角挖穿河底的岩石来筑巢，/是为了防止;产下的卵被水流冲走。@</t>
+          <t>金鱼王之所以会用角;挖穿河底的岩石来筑巢，/是为了防止;产下的卵被水流冲走。@</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -10673,7 +10673,7 @@
       <c r="G178" s="5" t="n"/>
       <c r="H178" s="1" t="inlineStr">
         <is>
-          <t>在南美流;传着这样的说法，/它的右眼一直看着未来，;左眼一直看着过去。@</t>
+          <t>在南美流传着;这样的说法，/它的右眼一直看着未来，;左眼一直看着过去。@</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
